--- a/business_surveys/027_smart_home_feature_value_survey--business_surveys.xlsx
+++ b/business_surveys/027_smart_home_feature_value_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -790,7 +790,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How interested are you in Smart Home Features?</t>
+          <t>Smart Home Feature Interest</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How important are Smart Home Features?</t>
+          <t>Smart Home Feature Importance</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -854,12 +854,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>smart_home_feature_expectation</t>
+          <t>smart_home_feature_expectation_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Smart Home Feature Expectation</t>
+          <t>Smart Home Feature Expectation 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -910,7 +910,7 @@
   <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1632,7 +1632,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>smart_home_feature_expectation_choices</t>
+          <t>smart_home_feature_expectation_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1649,7 +1649,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>smart_home_feature_expectation_choices</t>
+          <t>smart_home_feature_expectation_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>smart_home_feature_expectation_choices</t>
+          <t>smart_home_feature_expectation_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1683,7 +1683,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>smart_home_feature_expectation_choices</t>
+          <t>smart_home_feature_expectation_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>smart_home_feature_expectation_choices</t>
+          <t>smart_home_feature_expectation_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
